--- a/research/traditional_assets/database/data/slovenia/slovenia_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_investments_asset_management.xlsx
@@ -587,35 +587,17 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.447</v>
-      </c>
-      <c r="G2">
-        <v>0.1570754716981132</v>
-      </c>
-      <c r="H2">
-        <v>0.1570754716981132</v>
-      </c>
-      <c r="I2">
-        <v>0.1382075471698113</v>
-      </c>
-      <c r="J2">
-        <v>0.1382075471698113</v>
-      </c>
       <c r="K2">
-        <v>-2.83</v>
-      </c>
-      <c r="L2">
-        <v>-0.1334905660377358</v>
+        <v>5.59</v>
       </c>
       <c r="M2">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.1372161895360316</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-4.911660777385159</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,82 +606,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>13.9</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>11.8</v>
+        <v>0.064</v>
       </c>
       <c r="V2">
-        <v>0.1164856860809477</v>
+        <v>0.03216080402010051</v>
       </c>
       <c r="W2">
-        <v>-0.01800254452926209</v>
+        <v>0.2957671957671958</v>
       </c>
       <c r="X2">
-        <v>0.05507527811972474</v>
+        <v>0.1064176498333318</v>
       </c>
       <c r="Y2">
-        <v>-0.07307782264898682</v>
+        <v>0.189349545933864</v>
       </c>
       <c r="Z2">
-        <v>0.1448314967515388</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>0.02001680591896268</v>
+        <v>-0.02301806092356163</v>
       </c>
       <c r="AB2">
-        <v>0.05281307651374301</v>
+        <v>0.09870519060524001</v>
       </c>
       <c r="AC2">
-        <v>-0.03279627059478032</v>
+        <v>-0.1217232515288016</v>
       </c>
       <c r="AD2">
-        <v>8.94</v>
+        <v>1.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8.94</v>
+        <v>1.2</v>
       </c>
       <c r="AG2">
-        <v>-2.860000000000001</v>
+        <v>1.136</v>
       </c>
       <c r="AH2">
-        <v>0.08109579100145138</v>
+        <v>0.3761755485893417</v>
       </c>
       <c r="AI2">
-        <v>0.05032650303985589</v>
+        <v>0.04316546762589928</v>
       </c>
       <c r="AJ2">
-        <v>-0.02905323039414873</v>
+        <v>0.36340371081254</v>
       </c>
       <c r="AK2">
-        <v>-0.01724553786782442</v>
+        <v>0.04095760023074704</v>
       </c>
       <c r="AL2">
-        <v>0.9379999999999999</v>
+        <v>0.031</v>
       </c>
       <c r="AM2">
-        <v>0.9379999999999999</v>
+        <v>-6.079000000000001</v>
       </c>
       <c r="AN2">
-        <v>2.684684684684684</v>
+        <v>-2.61437908496732</v>
       </c>
       <c r="AO2">
-        <v>3.123667377398721</v>
+        <v>-14.80645161290323</v>
       </c>
       <c r="AP2">
-        <v>-0.8588588588588592</v>
+        <v>-2.474945533769063</v>
       </c>
       <c r="AQ2">
-        <v>3.123667377398721</v>
+        <v>0.07550583977627899</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +689,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KD, financna druzba, d. d. (LJSE:SKDR)</t>
+          <t>KS NALOZBE financne nalozbe d.d. (LJSE:KSFR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,35 +697,17 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.447</v>
-      </c>
-      <c r="G3">
-        <v>0.1570754716981132</v>
-      </c>
-      <c r="H3">
-        <v>0.1570754716981132</v>
-      </c>
-      <c r="I3">
-        <v>0.1382075471698113</v>
-      </c>
-      <c r="J3">
-        <v>0.1382075471698113</v>
-      </c>
       <c r="K3">
-        <v>-2.83</v>
-      </c>
-      <c r="L3">
-        <v>-0.1334905660377358</v>
+        <v>5.59</v>
       </c>
       <c r="M3">
-        <v>13.9</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.1372161895360316</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-4.911660777385159</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,82 +716,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>13.9</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>11.8</v>
+        <v>0.064</v>
       </c>
       <c r="V3">
-        <v>0.1164856860809477</v>
+        <v>0.03216080402010051</v>
       </c>
       <c r="W3">
-        <v>-0.01800254452926209</v>
+        <v>0.2957671957671958</v>
       </c>
       <c r="X3">
-        <v>0.05507527811972474</v>
+        <v>0.1064176498333318</v>
       </c>
       <c r="Y3">
-        <v>-0.07307782264898682</v>
+        <v>0.189349545933864</v>
       </c>
       <c r="Z3">
-        <v>0.1448314967515388</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.02001680591896268</v>
+        <v>-0.02301806092356163</v>
       </c>
       <c r="AB3">
-        <v>0.05281307651374301</v>
+        <v>0.09870519060524001</v>
       </c>
       <c r="AC3">
-        <v>-0.03279627059478032</v>
+        <v>-0.1217232515288016</v>
       </c>
       <c r="AD3">
-        <v>8.94</v>
+        <v>1.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8.94</v>
+        <v>1.2</v>
       </c>
       <c r="AG3">
-        <v>-2.860000000000001</v>
+        <v>1.136</v>
       </c>
       <c r="AH3">
-        <v>0.08109579100145138</v>
+        <v>0.3761755485893417</v>
       </c>
       <c r="AI3">
-        <v>0.05032650303985589</v>
+        <v>0.04316546762589928</v>
       </c>
       <c r="AJ3">
-        <v>-0.02905323039414873</v>
+        <v>0.36340371081254</v>
       </c>
       <c r="AK3">
-        <v>-0.01724553786782442</v>
+        <v>0.04095760023074704</v>
       </c>
       <c r="AL3">
-        <v>0.9379999999999999</v>
+        <v>0.031</v>
       </c>
       <c r="AM3">
-        <v>0.9379999999999999</v>
+        <v>-6.079000000000001</v>
       </c>
       <c r="AN3">
-        <v>2.684684684684684</v>
+        <v>-2.61437908496732</v>
       </c>
       <c r="AO3">
-        <v>3.123667377398721</v>
+        <v>-14.80645161290323</v>
       </c>
       <c r="AP3">
-        <v>-0.8588588588588592</v>
+        <v>-2.474945533769063</v>
       </c>
       <c r="AQ3">
-        <v>3.123667377398721</v>
+        <v>0.07550583977627899</v>
       </c>
     </row>
   </sheetData>
